--- a/forms/trg/Formulir_TRG_hospbiz.xlsx
+++ b/forms/trg/Formulir_TRG_hospbiz.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">

--- a/forms/trg/Formulir_TRG_hospbiz.xlsx
+++ b/forms/trg/Formulir_TRG_hospbiz.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Syahrir A. Pasinringi, MS</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
